--- a/data/CS1/case18_2/case18_operational_data.xlsx
+++ b/data/CS1/case18_2/case18_operational_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS1/case18/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS1/case18_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD08483-5A71-E844-8847-05F3B51DB09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF46B63-BE1A-E946-9262-3434814672DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="680" windowWidth="28400" windowHeight="18440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1000" yWindow="680" windowWidth="28400" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -454,10 +454,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>0.2</v>
+        <f>E2*3.5</f>
+        <v>0.70000000000000007</v>
       </c>
       <c r="C2" s="1">
-        <v>0.12</v>
+        <f>F2*1.5</f>
+        <v>0.18</v>
       </c>
       <c r="D2" s="2">
         <f>$B2/SUM($B$2:$B$1048576)</f>
@@ -475,13 +477,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>0.4</v>
+        <f t="shared" ref="B3:B16" si="0">E3*3.5</f>
+        <v>1.4000000000000001</v>
       </c>
       <c r="C3" s="1">
-        <v>0.25</v>
+        <f t="shared" ref="C3:C16" si="1">F3*1.5</f>
+        <v>0.375</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" ref="D3:D16" si="0">$B3/SUM($B$2:$B$1048576)</f>
+        <f t="shared" ref="D3:D16" si="2">$B3/SUM($B$2:$B$1048576)</f>
         <v>3.4482758620689655E-2</v>
       </c>
       <c r="E3" s="1">
@@ -496,13 +500,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>1.5</v>
+        <f t="shared" si="0"/>
+        <v>5.25</v>
       </c>
       <c r="C4" s="1">
-        <v>0.93</v>
+        <f t="shared" si="1"/>
+        <v>1.395</v>
       </c>
       <c r="D4" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.12931034482758622</v>
       </c>
       <c r="E4" s="1">
@@ -517,13 +523,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>10.5</v>
       </c>
       <c r="C5" s="1">
-        <v>2.2599999999999998</v>
+        <f t="shared" si="1"/>
+        <v>3.3899999999999997</v>
       </c>
       <c r="D5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.25862068965517243</v>
       </c>
       <c r="E5" s="1">
@@ -538,13 +546,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>0.8</v>
+        <f t="shared" si="0"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="C6" s="1">
-        <v>0.5</v>
+        <f t="shared" si="1"/>
+        <v>0.75</v>
       </c>
       <c r="D6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>6.8965517241379309E-2</v>
       </c>
       <c r="E6" s="1">
@@ -559,13 +569,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>0.2</v>
+        <f t="shared" si="0"/>
+        <v>0.70000000000000007</v>
       </c>
       <c r="C7" s="1">
-        <v>0.12</v>
+        <f t="shared" si="1"/>
+        <v>0.18</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.7241379310344827E-2</v>
       </c>
       <c r="E7" s="1">
@@ -580,14 +592,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>3.5</v>
       </c>
       <c r="C8" s="1">
-        <v>0.62</v>
+        <f t="shared" si="1"/>
+        <v>0.92999999999999994</v>
       </c>
       <c r="D8" s="2">
-        <f t="shared" si="0"/>
-        <v>8.6206896551724144E-2</v>
+        <f t="shared" si="2"/>
+        <v>8.620689655172413E-2</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -601,14 +615,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>0.5</v>
+        <f t="shared" si="0"/>
+        <v>1.75</v>
       </c>
       <c r="C9" s="1">
-        <v>0.31</v>
+        <f t="shared" si="1"/>
+        <v>0.46499999999999997</v>
       </c>
       <c r="D9" s="2">
-        <f t="shared" si="0"/>
-        <v>4.3103448275862072E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.3103448275862065E-2</v>
       </c>
       <c r="E9" s="1">
         <v>0.5</v>
@@ -622,14 +638,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>3.5</v>
       </c>
       <c r="C10" s="1">
-        <v>0.62</v>
+        <f t="shared" si="1"/>
+        <v>0.92999999999999994</v>
       </c>
       <c r="D10" s="2">
-        <f t="shared" si="0"/>
-        <v>8.6206896551724144E-2</v>
+        <f t="shared" si="2"/>
+        <v>8.620689655172413E-2</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -643,13 +661,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>0.3</v>
+        <f t="shared" si="0"/>
+        <v>1.05</v>
       </c>
       <c r="C11" s="1">
-        <v>0.19</v>
+        <f t="shared" si="1"/>
+        <v>0.28500000000000003</v>
       </c>
       <c r="D11" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.5862068965517241E-2</v>
       </c>
       <c r="E11" s="1">
@@ -664,13 +684,15 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>0.2</v>
+        <f t="shared" si="0"/>
+        <v>0.70000000000000007</v>
       </c>
       <c r="C12" s="1">
-        <v>0.12</v>
+        <f t="shared" si="1"/>
+        <v>0.18</v>
       </c>
       <c r="D12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.7241379310344827E-2</v>
       </c>
       <c r="E12" s="1">
@@ -685,13 +707,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>0.8</v>
+        <f t="shared" si="0"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="C13" s="1">
-        <v>0.5</v>
+        <f t="shared" si="1"/>
+        <v>0.75</v>
       </c>
       <c r="D13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>6.8965517241379309E-2</v>
       </c>
       <c r="E13" s="1">
@@ -706,14 +730,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>0.5</v>
+        <f t="shared" si="0"/>
+        <v>1.75</v>
       </c>
       <c r="C14" s="1">
-        <v>0.31</v>
+        <f t="shared" si="1"/>
+        <v>0.46499999999999997</v>
       </c>
       <c r="D14" s="2">
-        <f t="shared" si="0"/>
-        <v>4.3103448275862072E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.3103448275862065E-2</v>
       </c>
       <c r="E14" s="1">
         <v>0.5</v>
@@ -727,14 +753,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>3.5</v>
       </c>
       <c r="C15" s="1">
-        <v>0.62</v>
+        <f t="shared" si="1"/>
+        <v>0.92999999999999994</v>
       </c>
       <c r="D15" s="2">
-        <f t="shared" si="0"/>
-        <v>8.6206896551724144E-2</v>
+        <f t="shared" si="2"/>
+        <v>8.620689655172413E-2</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -748,13 +776,15 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>0.2</v>
+        <f t="shared" si="0"/>
+        <v>0.70000000000000007</v>
       </c>
       <c r="C16" s="1">
-        <v>0.12</v>
+        <f t="shared" si="1"/>
+        <v>0.18</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.7241379310344827E-2</v>
       </c>
       <c r="E16" s="1">
